--- a/Archivos de trabajo/Yami/elasticidades/itcrm_por_provincias MOA MOI.xlsx
+++ b/Archivos de trabajo/Yami/elasticidades/itcrm_por_provincias MOA MOI.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29912"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -15,7 +15,23 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="191028"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -116,7 +132,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -464,12 +480,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AC277"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:29" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -558,7 +574,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:29">
       <c r="A2" s="2">
         <v>37257</v>
       </c>
@@ -644,7 +660,7 @@
         <v>129.25969447708579</v>
       </c>
     </row>
-    <row r="3" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:29">
       <c r="A3" s="2">
         <v>37288</v>
       </c>
@@ -730,7 +746,7 @@
         <v>157.81433607520569</v>
       </c>
     </row>
-    <row r="4" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:29">
       <c r="A4" s="2">
         <v>37316</v>
       </c>
@@ -816,7 +832,7 @@
         <v>192.7144535840188</v>
       </c>
     </row>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:29">
       <c r="A5" s="2">
         <v>37347</v>
       </c>
@@ -902,7 +918,7 @@
         <v>214.80611045828451</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:29">
       <c r="A6" s="2">
         <v>37377</v>
       </c>
@@ -988,7 +1004,7 @@
         <v>224.67685076380729</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:29">
       <c r="A7" s="2">
         <v>37408</v>
       </c>
@@ -1074,7 +1090,7 @@
         <v>233.60752056404229</v>
       </c>
     </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:29">
       <c r="A8" s="2">
         <v>37438</v>
       </c>
@@ -1160,7 +1176,7 @@
         <v>220.56404230317281</v>
       </c>
     </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:29">
       <c r="A9" s="2">
         <v>37469</v>
       </c>
@@ -1246,7 +1262,7 @@
         <v>210.45828437132789</v>
       </c>
     </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:29">
       <c r="A10" s="2">
         <v>37500</v>
       </c>
@@ -1332,7 +1348,7 @@
         <v>204.4653349001176</v>
       </c>
     </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:29">
       <c r="A11" s="2">
         <v>37530</v>
       </c>
@@ -1418,7 +1434,7 @@
         <v>196.70975323149241</v>
       </c>
     </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:29">
       <c r="A12" s="2">
         <v>37561</v>
       </c>
@@ -1504,7 +1520,7 @@
         <v>194.94712103407761</v>
       </c>
     </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:29">
       <c r="A13" s="2">
         <v>37591</v>
       </c>
@@ -1590,7 +1606,7 @@
         <v>194.2420681551117</v>
       </c>
     </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:29">
       <c r="A14" s="2">
         <v>37622</v>
       </c>
@@ -1676,7 +1692,7 @@
         <v>185.89894242068161</v>
       </c>
     </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:29">
       <c r="A15" s="2">
         <v>37653</v>
       </c>
@@ -1762,7 +1778,7 @@
         <v>178.4958871915394</v>
       </c>
     </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:29">
       <c r="A16" s="2">
         <v>37681</v>
       </c>
@@ -1848,7 +1864,7 @@
         <v>175.4406580493538</v>
       </c>
     </row>
-    <row r="17" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:29">
       <c r="A17" s="2">
         <v>37712</v>
       </c>
@@ -1934,7 +1950,7 @@
         <v>171.09283196239721</v>
       </c>
     </row>
-    <row r="18" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:29">
       <c r="A18" s="2">
         <v>37742</v>
       </c>
@@ -2020,7 +2036,7 @@
         <v>174.85311398354881</v>
       </c>
     </row>
-    <row r="19" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:29">
       <c r="A19" s="2">
         <v>37773</v>
       </c>
@@ -2106,7 +2122,7 @@
         <v>175.2056404230317</v>
       </c>
     </row>
-    <row r="20" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:29">
       <c r="A20" s="2">
         <v>37803</v>
       </c>
@@ -2192,7 +2208,7 @@
         <v>173.20799059929499</v>
       </c>
     </row>
-    <row r="21" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:29">
       <c r="A21" s="2">
         <v>37834</v>
       </c>
@@ -2278,7 +2294,7 @@
         <v>177.6733254994125</v>
       </c>
     </row>
-    <row r="22" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:29">
       <c r="A22" s="2">
         <v>37865</v>
       </c>
@@ -2364,7 +2380,7 @@
         <v>180.14101057579319</v>
       </c>
     </row>
-    <row r="23" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:29">
       <c r="A23" s="2">
         <v>37895</v>
       </c>
@@ -2450,7 +2466,7 @@
         <v>179.4359576968273</v>
       </c>
     </row>
-    <row r="24" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:29">
       <c r="A24" s="2">
         <v>37926</v>
       </c>
@@ -2536,7 +2552,7 @@
         <v>180.61104582843711</v>
       </c>
     </row>
-    <row r="25" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:29">
       <c r="A25" s="2">
         <v>37956</v>
       </c>
@@ -2622,7 +2638,7 @@
         <v>187.77908343125739</v>
       </c>
     </row>
-    <row r="26" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:29">
       <c r="A26" s="2">
         <v>37987</v>
       </c>
@@ -2708,7 +2724,7 @@
         <v>187.5440658049354</v>
       </c>
     </row>
-    <row r="27" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:29">
       <c r="A27" s="2">
         <v>38018</v>
       </c>
@@ -2794,7 +2810,7 @@
         <v>188.3666274970623</v>
       </c>
     </row>
-    <row r="28" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:29">
       <c r="A28" s="2">
         <v>38047</v>
       </c>
@@ -2880,7 +2896,7 @@
         <v>184.72385428907171</v>
       </c>
     </row>
-    <row r="29" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:29">
       <c r="A29" s="2">
         <v>38078</v>
       </c>
@@ -2966,7 +2982,7 @@
         <v>178.84841363102231</v>
       </c>
     </row>
-    <row r="30" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:29">
       <c r="A30" s="2">
         <v>38108</v>
       </c>
@@ -3052,7 +3068,7 @@
         <v>179.20094007050531</v>
       </c>
     </row>
-    <row r="31" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:29">
       <c r="A31" s="2">
         <v>38139</v>
       </c>
@@ -3138,7 +3154,7 @@
         <v>181.31609870740311</v>
       </c>
     </row>
-    <row r="32" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:29">
       <c r="A32" s="2">
         <v>38169</v>
       </c>
@@ -3224,7 +3240,7 @@
         <v>183.07873090481789</v>
       </c>
     </row>
-    <row r="33" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:29">
       <c r="A33" s="2">
         <v>38200</v>
       </c>
@@ -3310,7 +3326,7 @@
         <v>187.30904817861341</v>
       </c>
     </row>
-    <row r="34" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:29">
       <c r="A34" s="2">
         <v>38231</v>
       </c>
@@ -3396,7 +3412,7 @@
         <v>188.3666274970623</v>
       </c>
     </row>
-    <row r="35" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:29">
       <c r="A35" s="2">
         <v>38261</v>
       </c>
@@ -3482,7 +3498,7 @@
         <v>188.48413631022331</v>
       </c>
     </row>
-    <row r="36" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:29">
       <c r="A36" s="2">
         <v>38292</v>
       </c>
@@ -3568,7 +3584,7 @@
         <v>191.42185663924801</v>
       </c>
     </row>
-    <row r="37" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:29">
       <c r="A37" s="2">
         <v>38322</v>
       </c>
@@ -3654,7 +3670,7 @@
         <v>196.12220916568739</v>
       </c>
     </row>
-    <row r="38" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:29">
       <c r="A38" s="2">
         <v>38353</v>
       </c>
@@ -3740,7 +3756,7 @@
         <v>192.7144535840188</v>
       </c>
     </row>
-    <row r="39" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:29">
       <c r="A39" s="2">
         <v>38384</v>
       </c>
@@ -3826,7 +3842,7 @@
         <v>191.304347826087</v>
       </c>
     </row>
-    <row r="40" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:29">
       <c r="A40" s="2">
         <v>38412</v>
       </c>
@@ -3912,7 +3928,7 @@
         <v>188.01410105757941</v>
       </c>
     </row>
-    <row r="41" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:29">
       <c r="A41" s="2">
         <v>38443</v>
       </c>
@@ -3998,7 +4014,7 @@
         <v>187.66157461809641</v>
       </c>
     </row>
-    <row r="42" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:29">
       <c r="A42" s="2">
         <v>38473</v>
       </c>
@@ -4084,7 +4100,7 @@
         <v>189.42420681551121</v>
       </c>
     </row>
-    <row r="43" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:29">
       <c r="A43" s="2">
         <v>38504</v>
       </c>
@@ -4170,7 +4186,7 @@
         <v>186.95652173913049</v>
       </c>
     </row>
-    <row r="44" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:29">
       <c r="A44" s="2">
         <v>38534</v>
       </c>
@@ -4256,7 +4272,7 @@
         <v>185.54641598119861</v>
       </c>
     </row>
-    <row r="45" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:29">
       <c r="A45" s="2">
         <v>38565</v>
       </c>
@@ -4342,7 +4358,7 @@
         <v>188.01410105757941</v>
       </c>
     </row>
-    <row r="46" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:29">
       <c r="A46" s="2">
         <v>38596</v>
       </c>
@@ -4428,7 +4444,7 @@
         <v>190.71680376028209</v>
       </c>
     </row>
-    <row r="47" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:29">
       <c r="A47" s="2">
         <v>38626</v>
       </c>
@@ -4514,7 +4530,7 @@
         <v>193.30199764982379</v>
       </c>
     </row>
-    <row r="48" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:29">
       <c r="A48" s="2">
         <v>38657</v>
       </c>
@@ -4600,7 +4616,7 @@
         <v>192.2444183313749</v>
       </c>
     </row>
-    <row r="49" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:29">
       <c r="A49" s="2">
         <v>38687</v>
       </c>
@@ -4686,7 +4702,7 @@
         <v>192.12690951821389</v>
       </c>
     </row>
-    <row r="50" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:29">
       <c r="A50" s="2">
         <v>38718</v>
       </c>
@@ -4772,7 +4788,7 @@
         <v>193.77203290246771</v>
       </c>
     </row>
-    <row r="51" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:29">
       <c r="A51" s="2">
         <v>38749</v>
       </c>
@@ -4858,7 +4874,7 @@
         <v>197.1797884841364</v>
       </c>
     </row>
-    <row r="52" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:29">
       <c r="A52" s="2">
         <v>38777</v>
       </c>
@@ -4944,7 +4960,7 @@
         <v>197.0622796709753</v>
       </c>
     </row>
-    <row r="53" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:29">
       <c r="A53" s="2">
         <v>38808</v>
       </c>
@@ -5030,7 +5046,7 @@
         <v>196.5922444183314</v>
       </c>
     </row>
-    <row r="54" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:29">
       <c r="A54" s="2">
         <v>38838</v>
       </c>
@@ -5116,7 +5132,7 @@
         <v>195.6521739130435</v>
       </c>
     </row>
-    <row r="55" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:29">
       <c r="A55" s="2">
         <v>38869</v>
       </c>
@@ -5202,7 +5218,7 @@
         <v>193.0669800235018</v>
       </c>
     </row>
-    <row r="56" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:29">
       <c r="A56" s="2">
         <v>38899</v>
       </c>
@@ -5288,7 +5304,7 @@
         <v>194.71210340775559</v>
       </c>
     </row>
-    <row r="57" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:29">
       <c r="A57" s="2">
         <v>38930</v>
       </c>
@@ -5374,7 +5390,7 @@
         <v>195.41715628672151</v>
       </c>
     </row>
-    <row r="58" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:29">
       <c r="A58" s="2">
         <v>38961</v>
       </c>
@@ -5460,7 +5476,7 @@
         <v>194.94712103407761</v>
       </c>
     </row>
-    <row r="59" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:29">
       <c r="A59" s="2">
         <v>38991</v>
       </c>
@@ -5546,7 +5562,7 @@
         <v>193.6545240893067</v>
       </c>
     </row>
-    <row r="60" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:29">
       <c r="A60" s="2">
         <v>39022</v>
       </c>
@@ -5632,7 +5648,7 @@
         <v>191.77438307873089</v>
       </c>
     </row>
-    <row r="61" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:29">
       <c r="A61" s="2">
         <v>39052</v>
       </c>
@@ -5718,7 +5734,7 @@
         <v>191.18683901292599</v>
       </c>
     </row>
-    <row r="62" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:29">
       <c r="A62" s="2">
         <v>39083</v>
       </c>
@@ -5804,7 +5820,7 @@
         <v>190.71680376028209</v>
       </c>
     </row>
-    <row r="63" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:29">
       <c r="A63" s="2">
         <v>39114</v>
       </c>
@@ -5890,7 +5906,7 @@
         <v>192.47943595769689</v>
       </c>
     </row>
-    <row r="64" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:29">
       <c r="A64" s="2">
         <v>39142</v>
       </c>
@@ -5976,7 +5992,7 @@
         <v>192.3619271445358</v>
       </c>
     </row>
-    <row r="65" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:29">
       <c r="A65" s="2">
         <v>39173</v>
       </c>
@@ -6062,7 +6078,7 @@
         <v>192.47943595769689</v>
       </c>
     </row>
-    <row r="66" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:29">
       <c r="A66" s="2">
         <v>39203</v>
       </c>
@@ -6148,7 +6164,7 @@
         <v>190.4817861339601</v>
       </c>
     </row>
-    <row r="67" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:29">
       <c r="A67" s="2">
         <v>39234</v>
       </c>
@@ -6234,7 +6250,7 @@
         <v>188.01410105757941</v>
       </c>
     </row>
-    <row r="68" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:29">
       <c r="A68" s="2">
         <v>39264</v>
       </c>
@@ -6320,7 +6336,7 @@
         <v>188.83666274970619</v>
       </c>
     </row>
-    <row r="69" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:29">
       <c r="A69" s="2">
         <v>39295</v>
       </c>
@@ -6406,7 +6422,7 @@
         <v>184.01880141010579</v>
       </c>
     </row>
-    <row r="70" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:29">
       <c r="A70" s="2">
         <v>39326</v>
       </c>
@@ -6492,7 +6508,7 @@
         <v>182.60869565217391</v>
       </c>
     </row>
-    <row r="71" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:29">
       <c r="A71" s="2">
         <v>39356</v>
       </c>
@@ -6578,7 +6594,7 @@
         <v>186.01645123384259</v>
       </c>
     </row>
-    <row r="72" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:29">
       <c r="A72" s="2">
         <v>39387</v>
       </c>
@@ -6664,7 +6680,7 @@
         <v>187.07403055229139</v>
       </c>
     </row>
-    <row r="73" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:29">
       <c r="A73" s="2">
         <v>39417</v>
       </c>
@@ -6750,7 +6766,7 @@
         <v>186.95652173913049</v>
       </c>
     </row>
-    <row r="74" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:29">
       <c r="A74" s="2">
         <v>39448</v>
       </c>
@@ -6836,7 +6852,7 @@
         <v>187.1915393654524</v>
       </c>
     </row>
-    <row r="75" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:29">
       <c r="A75" s="2">
         <v>39479</v>
       </c>
@@ -6922,7 +6938,7 @@
         <v>187.30904817861341</v>
       </c>
     </row>
-    <row r="76" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:29">
       <c r="A76" s="2">
         <v>39508</v>
       </c>
@@ -7008,7 +7024,7 @@
         <v>186.95652173913049</v>
       </c>
     </row>
-    <row r="77" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:29">
       <c r="A77" s="2">
         <v>39539</v>
       </c>
@@ -7094,7 +7110,7 @@
         <v>183.4312573443008</v>
       </c>
     </row>
-    <row r="78" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:29">
       <c r="A78" s="2">
         <v>39569</v>
       </c>
@@ -7180,7 +7196,7 @@
         <v>180.61104582843711</v>
       </c>
     </row>
-    <row r="79" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:29">
       <c r="A79" s="2">
         <v>39600</v>
       </c>
@@ -7266,7 +7282,7 @@
         <v>174.50058754406581</v>
       </c>
     </row>
-    <row r="80" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:29">
       <c r="A80" s="2">
         <v>39630</v>
       </c>
@@ -7352,7 +7368,7 @@
         <v>172.73795534665101</v>
       </c>
     </row>
-    <row r="81" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:29">
       <c r="A81" s="2">
         <v>39661</v>
       </c>
@@ -7438,7 +7454,7 @@
         <v>168.74265569917739</v>
       </c>
     </row>
-    <row r="82" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:29">
       <c r="A82" s="2">
         <v>39692</v>
       </c>
@@ -7524,7 +7540,7 @@
         <v>161.45710928319619</v>
       </c>
     </row>
-    <row r="83" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:29">
       <c r="A83" s="2">
         <v>39722</v>
       </c>
@@ -7610,7 +7626,7 @@
         <v>150.64629847238541</v>
       </c>
     </row>
-    <row r="84" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:29">
       <c r="A84" s="2">
         <v>39753</v>
       </c>
@@ -7696,7 +7712,7 @@
         <v>149.82373678025851</v>
       </c>
     </row>
-    <row r="85" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:29">
       <c r="A85" s="2">
         <v>39783</v>
       </c>
@@ -7782,7 +7798,7 @@
         <v>151.7038777908343</v>
       </c>
     </row>
-    <row r="86" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:29">
       <c r="A86" s="2">
         <v>39814</v>
       </c>
@@ -7868,7 +7884,7 @@
         <v>154.17156286721499</v>
       </c>
     </row>
-    <row r="87" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:29">
       <c r="A87" s="2">
         <v>39845</v>
       </c>
@@ -7954,7 +7970,7 @@
         <v>154.40658049353709</v>
       </c>
     </row>
-    <row r="88" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:29">
       <c r="A88" s="2">
         <v>39873</v>
       </c>
@@ -8040,7 +8056,7 @@
         <v>159.57696827262049</v>
       </c>
     </row>
-    <row r="89" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:29">
       <c r="A89" s="2">
         <v>39904</v>
       </c>
@@ -8126,7 +8142,7 @@
         <v>161.80963572267919</v>
       </c>
     </row>
-    <row r="90" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:29">
       <c r="A90" s="2">
         <v>39934</v>
       </c>
@@ -8212,7 +8228,7 @@
         <v>167.4500587544066</v>
       </c>
     </row>
-    <row r="91" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:29">
       <c r="A91" s="2">
         <v>39965</v>
       </c>
@@ -8298,7 +8314,7 @@
         <v>173.5605170387779</v>
       </c>
     </row>
-    <row r="92" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:29">
       <c r="A92" s="2">
         <v>39995</v>
       </c>
@@ -8384,7 +8400,7 @@
         <v>175.32314923619271</v>
       </c>
     </row>
-    <row r="93" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:29">
       <c r="A93" s="2">
         <v>40026</v>
       </c>
@@ -8470,7 +8486,7 @@
         <v>178.2608695652174</v>
       </c>
     </row>
-    <row r="94" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:29">
       <c r="A94" s="2">
         <v>40057</v>
       </c>
@@ -8556,7 +8572,7 @@
         <v>177.55581668625149</v>
       </c>
     </row>
-    <row r="95" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:29">
       <c r="A95" s="2">
         <v>40087</v>
       </c>
@@ -8642,7 +8658,7 @@
         <v>178.1433607520564</v>
       </c>
     </row>
-    <row r="96" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:29">
       <c r="A96" s="2">
         <v>40118</v>
       </c>
@@ -8728,7 +8744,7 @@
         <v>176.8507638072856</v>
       </c>
     </row>
-    <row r="97" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:29">
       <c r="A97" s="2">
         <v>40148</v>
       </c>
@@ -8814,7 +8830,7 @@
         <v>171.91539365452411</v>
       </c>
     </row>
-    <row r="98" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:29">
       <c r="A98" s="2">
         <v>40179</v>
       </c>
@@ -8900,7 +8916,7 @@
         <v>166.15746180963569</v>
       </c>
     </row>
-    <row r="99" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:29">
       <c r="A99" s="2">
         <v>40210</v>
       </c>
@@ -8986,7 +9002,7 @@
         <v>159.45945945945951</v>
       </c>
     </row>
-    <row r="100" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:29">
       <c r="A100" s="2">
         <v>40238</v>
       </c>
@@ -9072,7 +9088,7 @@
         <v>157.10928319623969</v>
       </c>
     </row>
-    <row r="101" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:29">
       <c r="A101" s="2">
         <v>40269</v>
       </c>
@@ -9158,7 +9174,7 @@
         <v>155.81668625146889</v>
       </c>
     </row>
-    <row r="102" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:29">
       <c r="A102" s="2">
         <v>40299</v>
       </c>
@@ -9244,7 +9260,7 @@
         <v>150.64629847238541</v>
       </c>
     </row>
-    <row r="103" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:29">
       <c r="A103" s="2">
         <v>40330</v>
       </c>
@@ -9330,7 +9346,7 @@
         <v>148.76615746180971</v>
       </c>
     </row>
-    <row r="104" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:29">
       <c r="A104" s="2">
         <v>40360</v>
       </c>
@@ -9416,7 +9432,7 @@
         <v>150.41128084606339</v>
       </c>
     </row>
-    <row r="105" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:29">
       <c r="A105" s="2">
         <v>40391</v>
       </c>
@@ -9502,7 +9518,7 @@
         <v>150.0587544065805</v>
       </c>
     </row>
-    <row r="106" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:29">
       <c r="A106" s="2">
         <v>40422</v>
       </c>
@@ -9588,7 +9604,7 @@
         <v>151.2338425381904</v>
       </c>
     </row>
-    <row r="107" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:29">
       <c r="A107" s="2">
         <v>40452</v>
       </c>
@@ -9674,7 +9690,7 @@
         <v>152.17391304347831</v>
       </c>
     </row>
-    <row r="108" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:29">
       <c r="A108" s="2">
         <v>40483</v>
       </c>
@@ -9760,7 +9776,7 @@
         <v>148.06110458284371</v>
       </c>
     </row>
-    <row r="109" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:29">
       <c r="A109" s="2">
         <v>40513</v>
       </c>
@@ -9846,7 +9862,7 @@
         <v>146.29847238542891</v>
       </c>
     </row>
-    <row r="110" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:29">
       <c r="A110" s="2">
         <v>40544</v>
       </c>
@@ -9932,7 +9948,7 @@
         <v>146.41598119858989</v>
       </c>
     </row>
-    <row r="111" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:29">
       <c r="A111" s="2">
         <v>40575</v>
       </c>
@@ -10018,7 +10034,7 @@
         <v>148.6486486486487</v>
       </c>
     </row>
-    <row r="112" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:29">
       <c r="A112" s="2">
         <v>40603</v>
       </c>
@@ -10104,7 +10120,7 @@
         <v>148.6486486486487</v>
       </c>
     </row>
-    <row r="113" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:29">
       <c r="A113" s="2">
         <v>40634</v>
       </c>
@@ -10190,7 +10206,7 @@
         <v>150.64629847238541</v>
       </c>
     </row>
-    <row r="114" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:29">
       <c r="A114" s="2">
         <v>40664</v>
       </c>
@@ -10276,7 +10292,7 @@
         <v>147.82608695652169</v>
       </c>
     </row>
-    <row r="115" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:29">
       <c r="A115" s="2">
         <v>40695</v>
       </c>
@@ -10362,7 +10378,7 @@
         <v>147.23854289071679</v>
       </c>
     </row>
-    <row r="116" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:29">
       <c r="A116" s="2">
         <v>40725</v>
       </c>
@@ -10448,7 +10464,7 @@
         <v>147.59106933019979</v>
       </c>
     </row>
-    <row r="117" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:29">
       <c r="A117" s="2">
         <v>40756</v>
       </c>
@@ -10534,7 +10550,7 @@
         <v>145.12338425381901</v>
       </c>
     </row>
-    <row r="118" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:29">
       <c r="A118" s="2">
         <v>40787</v>
       </c>
@@ -10620,7 +10636,7 @@
         <v>137.13278495887201</v>
       </c>
     </row>
-    <row r="119" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:29">
       <c r="A119" s="2">
         <v>40817</v>
       </c>
@@ -10706,7 +10722,7 @@
         <v>134.07755581668621</v>
       </c>
     </row>
-    <row r="120" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:29">
       <c r="A120" s="2">
         <v>40848</v>
       </c>
@@ -10792,7 +10808,7 @@
         <v>132.9024676850764</v>
       </c>
     </row>
-    <row r="121" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:29">
       <c r="A121" s="2">
         <v>40878</v>
       </c>
@@ -10878,7 +10894,7 @@
         <v>129.7297297297298</v>
       </c>
     </row>
-    <row r="122" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:29">
       <c r="A122" s="2">
         <v>40909</v>
       </c>
@@ -10964,7 +10980,7 @@
         <v>130.55229142185661</v>
       </c>
     </row>
-    <row r="123" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:29">
       <c r="A123" s="2">
         <v>40940</v>
       </c>
@@ -11050,7 +11066,7 @@
         <v>133.7250293772033</v>
       </c>
     </row>
-    <row r="124" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:29">
       <c r="A124" s="2">
         <v>40969</v>
       </c>
@@ -11136,7 +11152,7 @@
         <v>129.02467685076391</v>
       </c>
     </row>
-    <row r="125" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:29">
       <c r="A125" s="2">
         <v>41000</v>
       </c>
@@ -11222,7 +11238,7 @@
         <v>125.6169212690952</v>
       </c>
     </row>
-    <row r="126" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:29">
       <c r="A126" s="2">
         <v>41030</v>
       </c>
@@ -11308,7 +11324,7 @@
         <v>120.5640423031727</v>
       </c>
     </row>
-    <row r="127" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:29">
       <c r="A127" s="2">
         <v>41061</v>
       </c>
@@ -11394,7 +11410,7 @@
         <v>117.86133960047</v>
       </c>
     </row>
-    <row r="128" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:29">
       <c r="A128" s="2">
         <v>41091</v>
       </c>
@@ -11480,7 +11496,7 @@
         <v>117.6263219741481</v>
       </c>
     </row>
-    <row r="129" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:29">
       <c r="A129" s="2">
         <v>41122</v>
       </c>
@@ -11566,7 +11582,7 @@
         <v>118.09635722679199</v>
       </c>
     </row>
-    <row r="130" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:29">
       <c r="A130" s="2">
         <v>41153</v>
       </c>
@@ -11652,7 +11668,7 @@
         <v>119.27144535840191</v>
       </c>
     </row>
-    <row r="131" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:29">
       <c r="A131" s="2">
         <v>41183</v>
       </c>
@@ -11738,7 +11754,7 @@
         <v>119.62397179788481</v>
       </c>
     </row>
-    <row r="132" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:29">
       <c r="A132" s="2">
         <v>41214</v>
       </c>
@@ -11824,7 +11840,7 @@
         <v>118.331374853114</v>
       </c>
     </row>
-    <row r="133" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:29">
       <c r="A133" s="2">
         <v>41244</v>
       </c>
@@ -11910,7 +11926,7 @@
         <v>119.1539365452409</v>
       </c>
     </row>
-    <row r="134" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:29">
       <c r="A134" s="2">
         <v>41275</v>
       </c>
@@ -11996,7 +12012,7 @@
         <v>120.4465334900118</v>
       </c>
     </row>
-    <row r="135" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:29">
       <c r="A135" s="2">
         <v>41306</v>
       </c>
@@ -12082,7 +12098,7 @@
         <v>121.6216216216216</v>
       </c>
     </row>
-    <row r="136" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:29">
       <c r="A136" s="2">
         <v>41334</v>
       </c>
@@ -12168,7 +12184,7 @@
         <v>120.68155111633379</v>
       </c>
     </row>
-    <row r="137" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:29">
       <c r="A137" s="2">
         <v>41365</v>
       </c>
@@ -12254,7 +12270,7 @@
         <v>120.0940070505288</v>
       </c>
     </row>
-    <row r="138" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:29">
       <c r="A138" s="2">
         <v>41395</v>
       </c>
@@ -12340,7 +12356,7 @@
         <v>119.0364277320799</v>
       </c>
     </row>
-    <row r="139" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:29">
       <c r="A139" s="2">
         <v>41426</v>
       </c>
@@ -12426,7 +12442,7 @@
         <v>116.4512338425382</v>
       </c>
     </row>
-    <row r="140" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:29">
       <c r="A140" s="2">
         <v>41456</v>
       </c>
@@ -12512,7 +12528,7 @@
         <v>114.3360752056404</v>
       </c>
     </row>
-    <row r="141" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:29">
       <c r="A141" s="2">
         <v>41487</v>
       </c>
@@ -12598,7 +12614,7 @@
         <v>113.8660399529965</v>
       </c>
     </row>
-    <row r="142" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:29">
       <c r="A142" s="2">
         <v>41518</v>
       </c>
@@ -12684,7 +12700,7 @@
         <v>116.2162162162163</v>
       </c>
     </row>
-    <row r="143" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:29">
       <c r="A143" s="2">
         <v>41548</v>
       </c>
@@ -12770,7 +12786,7 @@
         <v>118.09635722679199</v>
       </c>
     </row>
-    <row r="144" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:29">
       <c r="A144" s="2">
         <v>41579</v>
       </c>
@@ -12856,7 +12872,7 @@
         <v>115.8636897767333</v>
       </c>
     </row>
-    <row r="145" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:29">
       <c r="A145" s="2">
         <v>41609</v>
       </c>
@@ -12942,7 +12958,7 @@
         <v>118.683901292597</v>
       </c>
     </row>
-    <row r="146" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:29">
       <c r="A146" s="2">
         <v>41640</v>
       </c>
@@ -13028,7 +13044,7 @@
         <v>127.144535840188</v>
       </c>
     </row>
-    <row r="147" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:29">
       <c r="A147" s="2">
         <v>41671</v>
       </c>
@@ -13114,7 +13130,7 @@
         <v>134.9001175088132</v>
       </c>
     </row>
-    <row r="148" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:29">
       <c r="A148" s="2">
         <v>41699</v>
       </c>
@@ -13200,7 +13216,7 @@
         <v>131.84488836662749</v>
       </c>
     </row>
-    <row r="149" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:29">
       <c r="A149" s="2">
         <v>41730</v>
       </c>
@@ -13286,7 +13302,7 @@
         <v>131.1398354876616</v>
       </c>
     </row>
-    <row r="150" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:29">
       <c r="A150" s="2">
         <v>41760</v>
       </c>
@@ -13372,7 +13388,7 @@
         <v>129.02467685076391</v>
       </c>
     </row>
-    <row r="151" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:29">
       <c r="A151" s="2">
         <v>41791</v>
       </c>
@@ -13458,7 +13474,7 @@
         <v>127.497062279671</v>
       </c>
     </row>
-    <row r="152" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:29">
       <c r="A152" s="2">
         <v>41821</v>
       </c>
@@ -13544,7 +13560,7 @@
         <v>125.85193889541721</v>
       </c>
     </row>
-    <row r="153" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:29">
       <c r="A153" s="2">
         <v>41852</v>
       </c>
@@ -13630,7 +13646,7 @@
         <v>124.2068155111634</v>
       </c>
     </row>
-    <row r="154" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:29">
       <c r="A154" s="2">
         <v>41883</v>
       </c>
@@ -13716,7 +13732,7 @@
         <v>120.4465334900118</v>
       </c>
     </row>
-    <row r="155" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:29">
       <c r="A155" s="2">
         <v>41913</v>
       </c>
@@ -13802,7 +13818,7 @@
         <v>116.33372502937721</v>
       </c>
     </row>
-    <row r="156" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:29">
       <c r="A156" s="2">
         <v>41944</v>
       </c>
@@ -13888,7 +13904,7 @@
         <v>112.8084606345476</v>
       </c>
     </row>
-    <row r="157" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:29">
       <c r="A157" s="2">
         <v>41974</v>
       </c>
@@ -13974,7 +13990,7 @@
         <v>109.283196239718</v>
       </c>
     </row>
-    <row r="158" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:29">
       <c r="A158" s="2">
         <v>42005</v>
       </c>
@@ -14060,7 +14076,7 @@
         <v>107.2855464159812</v>
       </c>
     </row>
-    <row r="159" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:29">
       <c r="A159" s="2">
         <v>42036</v>
       </c>
@@ -14146,7 +14162,7 @@
         <v>104.23031727379551</v>
       </c>
     </row>
-    <row r="160" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:29">
       <c r="A160" s="2">
         <v>42064</v>
       </c>
@@ -14232,7 +14248,7 @@
         <v>99.412455934195066</v>
       </c>
     </row>
-    <row r="161" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:29">
       <c r="A161" s="2">
         <v>42095</v>
       </c>
@@ -14318,7 +14334,7 @@
         <v>99.764982373678038</v>
       </c>
     </row>
-    <row r="162" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:29">
       <c r="A162" s="2">
         <v>42125</v>
       </c>
@@ -14404,7 +14420,7 @@
         <v>99.647473560517042</v>
       </c>
     </row>
-    <row r="163" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:29">
       <c r="A163" s="2">
         <v>42156</v>
       </c>
@@ -14490,7 +14506,7 @@
         <v>98.707403055229165</v>
       </c>
     </row>
-    <row r="164" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:29">
       <c r="A164" s="2">
         <v>42186</v>
       </c>
@@ -14576,7 +14592,7 @@
         <v>96.709753231492385</v>
       </c>
     </row>
-    <row r="165" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:29">
       <c r="A165" s="2">
         <v>42217</v>
       </c>
@@ -14662,7 +14678,7 @@
         <v>93.184488836662766</v>
       </c>
     </row>
-    <row r="166" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:29">
       <c r="A166" s="2">
         <v>42248</v>
       </c>
@@ -14748,7 +14764,7 @@
         <v>89.541715628672165</v>
       </c>
     </row>
-    <row r="167" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:29">
       <c r="A167" s="2">
         <v>42278</v>
       </c>
@@ -14834,7 +14850,7 @@
         <v>89.42420681551117</v>
       </c>
     </row>
-    <row r="168" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:29">
       <c r="A168" s="2">
         <v>42309</v>
       </c>
@@ -14920,7 +14936,7 @@
         <v>88.601645123384273</v>
       </c>
     </row>
-    <row r="169" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:29">
       <c r="A169" s="2">
         <v>42339</v>
       </c>
@@ -15006,7 +15022,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="170" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:29">
       <c r="A170" s="2">
         <v>42370</v>
       </c>
@@ -15092,7 +15108,7 @@
         <v>112.8084606345476</v>
       </c>
     </row>
-    <row r="171" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:29">
       <c r="A171" s="2">
         <v>42401</v>
       </c>
@@ -15178,7 +15194,7 @@
         <v>120.4465334900118</v>
       </c>
     </row>
-    <row r="172" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:29">
       <c r="A172" s="2">
         <v>42430</v>
       </c>
@@ -15264,7 +15280,7 @@
         <v>121.03407755581669</v>
       </c>
     </row>
-    <row r="173" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:29">
       <c r="A173" s="2">
         <v>42461</v>
       </c>
@@ -15350,7 +15366,7 @@
         <v>114.3360752056404</v>
       </c>
     </row>
-    <row r="174" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:29">
       <c r="A174" s="2">
         <v>42491</v>
       </c>
@@ -15436,7 +15452,7 @@
         <v>107.2855464159812</v>
       </c>
     </row>
-    <row r="175" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:29">
       <c r="A175" s="2">
         <v>42522</v>
       </c>
@@ -15522,7 +15538,7 @@
         <v>104.8178613396005</v>
       </c>
     </row>
-    <row r="176" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:29">
       <c r="A176" s="2">
         <v>42552</v>
       </c>
@@ -15608,7 +15624,7 @@
         <v>108.93066980023509</v>
       </c>
     </row>
-    <row r="177" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:29">
       <c r="A177" s="2">
         <v>42583</v>
       </c>
@@ -15694,7 +15710,7 @@
         <v>108.813160987074</v>
       </c>
     </row>
-    <row r="178" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:29">
       <c r="A178" s="2">
         <v>42614</v>
       </c>
@@ -15780,7 +15796,7 @@
         <v>109.400705052879</v>
       </c>
     </row>
-    <row r="179" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:29">
       <c r="A179" s="2">
         <v>42644</v>
       </c>
@@ -15866,7 +15882,7 @@
         <v>107.9905992949471</v>
       </c>
     </row>
-    <row r="180" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:29">
       <c r="A180" s="2">
         <v>42675</v>
       </c>
@@ -15952,7 +15968,7 @@
         <v>104.4653349001175</v>
       </c>
     </row>
-    <row r="181" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:29">
       <c r="A181" s="2">
         <v>42705</v>
       </c>
@@ -16038,7 +16054,7 @@
         <v>105.5229142185664</v>
       </c>
     </row>
-    <row r="182" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:29">
       <c r="A182" s="2">
         <v>42736</v>
       </c>
@@ -16124,7 +16140,7 @@
         <v>106.46298472385431</v>
       </c>
     </row>
-    <row r="183" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:29">
       <c r="A183" s="2">
         <v>42767</v>
       </c>
@@ -16210,7 +16226,7 @@
         <v>104.23031727379551</v>
       </c>
     </row>
-    <row r="184" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:29">
       <c r="A184" s="2">
         <v>42795</v>
       </c>
@@ -16296,7 +16312,7 @@
         <v>101.64512338425379</v>
       </c>
     </row>
-    <row r="185" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:29">
       <c r="A185" s="2">
         <v>42826</v>
       </c>
@@ -16382,7 +16398,7 @@
         <v>98.354876615746207</v>
       </c>
     </row>
-    <row r="186" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:29">
       <c r="A186" s="2">
         <v>42856</v>
       </c>
@@ -16468,7 +16484,7 @@
         <v>98.942420681551127</v>
       </c>
     </row>
-    <row r="187" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:29">
       <c r="A187" s="2">
         <v>42887</v>
       </c>
@@ -16554,7 +16570,7 @@
         <v>99.882491186839019</v>
       </c>
     </row>
-    <row r="188" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:29">
       <c r="A188" s="2">
         <v>42917</v>
       </c>
@@ -16640,7 +16656,7 @@
         <v>106.9330199764983</v>
       </c>
     </row>
-    <row r="189" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:29">
       <c r="A189" s="2">
         <v>42948</v>
       </c>
@@ -16726,7 +16742,7 @@
         <v>108.6956521739131</v>
       </c>
     </row>
-    <row r="190" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:29">
       <c r="A190" s="2">
         <v>42979</v>
       </c>
@@ -16812,7 +16828,7 @@
         <v>106.5804935370153</v>
       </c>
     </row>
-    <row r="191" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:29">
       <c r="A191" s="2">
         <v>43009</v>
       </c>
@@ -16898,7 +16914,7 @@
         <v>104.8178613396005</v>
       </c>
     </row>
-    <row r="192" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:29">
       <c r="A192" s="2">
         <v>43040</v>
       </c>
@@ -16984,7 +17000,7 @@
         <v>102.8202115158637</v>
       </c>
     </row>
-    <row r="193" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:29">
       <c r="A193" s="2">
         <v>43070</v>
       </c>
@@ -17070,7 +17086,7 @@
         <v>102.1151586368978</v>
       </c>
     </row>
-    <row r="194" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:29">
       <c r="A194" s="2">
         <v>43101</v>
       </c>
@@ -17156,7 +17172,7 @@
         <v>109.753231492362</v>
       </c>
     </row>
-    <row r="195" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:29">
       <c r="A195" s="2">
         <v>43132</v>
       </c>
@@ -17242,7 +17258,7 @@
         <v>112.8084606345476</v>
       </c>
     </row>
-    <row r="196" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:29">
       <c r="A196" s="2">
         <v>43160</v>
       </c>
@@ -17328,7 +17344,7 @@
         <v>112.22091656874269</v>
       </c>
     </row>
-    <row r="197" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:29">
       <c r="A197" s="2">
         <v>43191</v>
       </c>
@@ -17414,7 +17430,7 @@
         <v>108.22561692126909</v>
       </c>
     </row>
-    <row r="198" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:29">
       <c r="A198" s="2">
         <v>43221</v>
       </c>
@@ -17500,7 +17516,7 @@
         <v>119.1539365452409</v>
       </c>
     </row>
-    <row r="199" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:29">
       <c r="A199" s="2">
         <v>43252</v>
       </c>
@@ -17586,7 +17602,7 @@
         <v>128.5546415981199</v>
       </c>
     </row>
-    <row r="200" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:29">
       <c r="A200" s="2">
         <v>43282</v>
       </c>
@@ -17672,7 +17688,7 @@
         <v>128.5546415981199</v>
       </c>
     </row>
-    <row r="201" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:29">
       <c r="A201" s="2">
         <v>43313</v>
       </c>
@@ -17758,7 +17774,7 @@
         <v>133.13748531139839</v>
       </c>
     </row>
-    <row r="202" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:29">
       <c r="A202" s="2">
         <v>43344</v>
       </c>
@@ -17844,7 +17860,7 @@
         <v>160.63454759106941</v>
       </c>
     </row>
-    <row r="203" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:29">
       <c r="A203" s="2">
         <v>43374</v>
       </c>
@@ -17930,7 +17946,7 @@
         <v>148.88366627497061</v>
       </c>
     </row>
-    <row r="204" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:29">
       <c r="A204" s="2">
         <v>43405</v>
       </c>
@@ -18016,7 +18032,7 @@
         <v>139.48296122209169</v>
       </c>
     </row>
-    <row r="205" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:29">
       <c r="A205" s="2">
         <v>43435</v>
       </c>
@@ -18102,7 +18118,7 @@
         <v>139.95299647473561</v>
       </c>
     </row>
-    <row r="206" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:29">
       <c r="A206" s="2">
         <v>43466</v>
       </c>
@@ -18188,7 +18204,7 @@
         <v>136.78025851938901</v>
       </c>
     </row>
-    <row r="207" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:29">
       <c r="A207" s="2">
         <v>43497</v>
       </c>
@@ -18274,7 +18290,7 @@
         <v>136.78025851938901</v>
       </c>
     </row>
-    <row r="208" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:29">
       <c r="A208" s="2">
         <v>43525</v>
       </c>
@@ -18360,7 +18376,7 @@
         <v>140.54054054054049</v>
       </c>
     </row>
-    <row r="209" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:29">
       <c r="A209" s="2">
         <v>43556</v>
       </c>
@@ -18446,7 +18462,7 @@
         <v>141.0105757931845</v>
       </c>
     </row>
-    <row r="210" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:29">
       <c r="A210" s="2">
         <v>43586</v>
       </c>
@@ -18532,7 +18548,7 @@
         <v>140.1880141010576</v>
       </c>
     </row>
-    <row r="211" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:29">
       <c r="A211" s="2">
         <v>43617</v>
       </c>
@@ -18618,7 +18634,7 @@
         <v>134.66509988249121</v>
       </c>
     </row>
-    <row r="212" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:29">
       <c r="A212" s="2">
         <v>43647</v>
       </c>
@@ -18704,7 +18720,7 @@
         <v>128.90716803760279</v>
       </c>
     </row>
-    <row r="213" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:29">
       <c r="A213" s="2">
         <v>43678</v>
       </c>
@@ -18790,7 +18806,7 @@
         <v>149.9412455934195</v>
       </c>
     </row>
-    <row r="214" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:29">
       <c r="A214" s="2">
         <v>43709</v>
       </c>
@@ -18876,7 +18892,7 @@
         <v>153.4665099882491</v>
       </c>
     </row>
-    <row r="215" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:29">
       <c r="A215" s="2">
         <v>43739</v>
       </c>
@@ -18962,7 +18978,7 @@
         <v>152.4089306698003</v>
       </c>
     </row>
-    <row r="216" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:29">
       <c r="A216" s="2">
         <v>43770</v>
       </c>
@@ -19048,7 +19064,7 @@
         <v>149.1186839012926</v>
       </c>
     </row>
-    <row r="217" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:29">
       <c r="A217" s="2">
         <v>43800</v>
       </c>
@@ -19134,7 +19150,7 @@
         <v>145.12338425381901</v>
       </c>
     </row>
-    <row r="218" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:29">
       <c r="A218" s="2">
         <v>43831</v>
       </c>
@@ -19220,7 +19236,7 @@
         <v>141.8331374853114</v>
       </c>
     </row>
-    <row r="219" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:29">
       <c r="A219" s="2">
         <v>43862</v>
       </c>
@@ -19306,7 +19322,7 @@
         <v>139.6004700352527</v>
       </c>
     </row>
-    <row r="220" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:29">
       <c r="A220" s="2">
         <v>43891</v>
       </c>
@@ -19392,7 +19408,7 @@
         <v>134.43008225616919</v>
       </c>
     </row>
-    <row r="221" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:29">
       <c r="A221" s="2">
         <v>43922</v>
       </c>
@@ -19478,7 +19494,7 @@
         <v>131.02232667450059</v>
       </c>
     </row>
-    <row r="222" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:29">
       <c r="A222" s="2">
         <v>43952</v>
       </c>
@@ -19564,7 +19580,7 @@
         <v>131.25734430082261</v>
       </c>
     </row>
-    <row r="223" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:29">
       <c r="A223" s="2">
         <v>43983</v>
       </c>
@@ -19650,7 +19666,7 @@
         <v>136.89776733254999</v>
       </c>
     </row>
-    <row r="224" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:29">
       <c r="A224" s="2">
         <v>44013</v>
       </c>
@@ -19736,7 +19752,7 @@
         <v>138.54289071680381</v>
       </c>
     </row>
-    <row r="225" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:29">
       <c r="A225" s="2">
         <v>44044</v>
       </c>
@@ -19822,7 +19838,7 @@
         <v>139.71797884841371</v>
       </c>
     </row>
-    <row r="226" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:29">
       <c r="A226" s="2">
         <v>44075</v>
       </c>
@@ -19908,7 +19924,7 @@
         <v>140.54054054054049</v>
       </c>
     </row>
-    <row r="227" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:29">
       <c r="A227" s="2">
         <v>44105</v>
       </c>
@@ -19994,7 +20010,7 @@
         <v>138.77790834312569</v>
       </c>
     </row>
-    <row r="228" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:29">
       <c r="A228" s="2">
         <v>44136</v>
       </c>
@@ -20080,7 +20096,7 @@
         <v>140.54054054054049</v>
       </c>
     </row>
-    <row r="229" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:29">
       <c r="A229" s="2">
         <v>44166</v>
       </c>
@@ -20166,7 +20182,7 @@
         <v>144.7708578143361</v>
       </c>
     </row>
-    <row r="230" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:29">
       <c r="A230" s="2">
         <v>44197</v>
       </c>
@@ -20252,7 +20268,7 @@
         <v>144.30082256169209</v>
       </c>
     </row>
-    <row r="231" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:29">
       <c r="A231" s="2">
         <v>44228</v>
       </c>
@@ -20338,7 +20354,7 @@
         <v>143.71327849588721</v>
       </c>
     </row>
-    <row r="232" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:29">
       <c r="A232" s="2">
         <v>44256</v>
       </c>
@@ -20424,7 +20440,7 @@
         <v>139.83548766157469</v>
       </c>
     </row>
-    <row r="233" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:29">
       <c r="A233" s="2">
         <v>44287</v>
       </c>
@@ -20510,7 +20526,7 @@
         <v>137.25029377203299</v>
       </c>
     </row>
-    <row r="234" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:29">
       <c r="A234" s="2">
         <v>44317</v>
       </c>
@@ -20596,7 +20612,7 @@
         <v>137.72032902467689</v>
       </c>
     </row>
-    <row r="235" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:29">
       <c r="A235" s="2">
         <v>44348</v>
       </c>
@@ -20682,7 +20698,7 @@
         <v>137.4853113983549</v>
       </c>
     </row>
-    <row r="236" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:29">
       <c r="A236" s="2">
         <v>44378</v>
       </c>
@@ -20768,7 +20784,7 @@
         <v>133.60752056404229</v>
       </c>
     </row>
-    <row r="237" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:29">
       <c r="A237" s="2">
         <v>44409</v>
       </c>
@@ -20854,7 +20870,7 @@
         <v>131.49236192714449</v>
       </c>
     </row>
-    <row r="238" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:29">
       <c r="A238" s="2">
         <v>44440</v>
       </c>
@@ -20940,7 +20956,7 @@
         <v>129.3772032902468</v>
       </c>
     </row>
-    <row r="239" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:29">
       <c r="A239" s="2">
         <v>44470</v>
       </c>
@@ -21026,7 +21042,7 @@
         <v>124.2068155111634</v>
       </c>
     </row>
-    <row r="240" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:29">
       <c r="A240" s="2">
         <v>44501</v>
       </c>
@@ -21112,7 +21128,7 @@
         <v>121.9741480611046</v>
       </c>
     </row>
-    <row r="241" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:29">
       <c r="A241" s="2">
         <v>44531</v>
       </c>
@@ -21198,7 +21214,7 @@
         <v>119.62397179788481</v>
       </c>
     </row>
-    <row r="242" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:29">
       <c r="A242" s="2">
         <v>44562</v>
       </c>
@@ -21284,7 +21300,7 @@
         <v>119.3889541715629</v>
       </c>
     </row>
-    <row r="243" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:29">
       <c r="A243" s="2">
         <v>44593</v>
       </c>
@@ -21370,7 +21386,7 @@
         <v>120.5640423031727</v>
       </c>
     </row>
-    <row r="244" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:29">
       <c r="A244" s="2">
         <v>44621</v>
       </c>
@@ -21456,7 +21472,7 @@
         <v>119.27144535840191</v>
       </c>
     </row>
-    <row r="245" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:29">
       <c r="A245" s="2">
         <v>44652</v>
       </c>
@@ -21542,7 +21558,7 @@
         <v>117.74383078730909</v>
       </c>
     </row>
-    <row r="246" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:29">
       <c r="A246" s="2">
         <v>44682</v>
       </c>
@@ -21628,7 +21644,7 @@
         <v>113.6310223266745</v>
       </c>
     </row>
-    <row r="247" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:29">
       <c r="A247" s="2">
         <v>44713</v>
       </c>
@@ -21714,7 +21730,7 @@
         <v>112.57344300822569</v>
       </c>
     </row>
-    <row r="248" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:29">
       <c r="A248" s="2">
         <v>44743</v>
       </c>
@@ -21800,7 +21816,7 @@
         <v>107.9905992949471</v>
       </c>
     </row>
-    <row r="249" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:29">
       <c r="A249" s="2">
         <v>44774</v>
       </c>
@@ -21886,7 +21902,7 @@
         <v>107.7555816686252</v>
       </c>
     </row>
-    <row r="250" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:29">
       <c r="A250" s="2">
         <v>44805</v>
       </c>
@@ -21972,7 +21988,7 @@
         <v>104.93537015276149</v>
       </c>
     </row>
-    <row r="251" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:29">
       <c r="A251" s="2">
         <v>44835</v>
       </c>
@@ -22058,7 +22074,7 @@
         <v>103.87779083431261</v>
       </c>
     </row>
-    <row r="252" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:29">
       <c r="A252" s="2">
         <v>44866</v>
       </c>
@@ -22144,7 +22160,7 @@
         <v>105.8754406580493</v>
       </c>
     </row>
-    <row r="253" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:29">
       <c r="A253" s="2">
         <v>44896</v>
       </c>
@@ -22230,7 +22246,7 @@
         <v>109.51821386604</v>
       </c>
     </row>
-    <row r="254" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:29">
       <c r="A254" s="2">
         <v>44927</v>
       </c>
@@ -22316,7 +22332,7 @@
         <v>111.7508813160987</v>
       </c>
     </row>
-    <row r="255" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:29">
       <c r="A255" s="2">
         <v>44958</v>
       </c>
@@ -22402,7 +22418,7 @@
         <v>111.3983548766158</v>
       </c>
     </row>
-    <row r="256" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:29">
       <c r="A256" s="2">
         <v>44986</v>
       </c>
@@ -22488,7 +22504,7 @@
         <v>109.9882491186839</v>
       </c>
     </row>
-    <row r="257" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:29">
       <c r="A257" s="2">
         <v>45017</v>
       </c>
@@ -22574,7 +22590,7 @@
         <v>110.2232667450059</v>
       </c>
     </row>
-    <row r="258" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:29">
       <c r="A258" s="2">
         <v>45047</v>
       </c>
@@ -22660,7 +22676,7 @@
         <v>109.400705052879</v>
       </c>
     </row>
-    <row r="259" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:29">
       <c r="A259" s="2">
         <v>45078</v>
       </c>
@@ -22746,7 +22762,7 @@
         <v>110.45828437132791</v>
       </c>
     </row>
-    <row r="260" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:29">
       <c r="A260" s="2">
         <v>45108</v>
       </c>
@@ -22832,7 +22848,7 @@
         <v>112.69095182138661</v>
       </c>
     </row>
-    <row r="261" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:29">
       <c r="A261" s="2">
         <v>45139</v>
       </c>
@@ -22918,7 +22934,7 @@
         <v>123.1492361927145</v>
       </c>
     </row>
-    <row r="262" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:29">
       <c r="A262" s="2">
         <v>45170</v>
       </c>
@@ -23004,7 +23020,7 @@
         <v>118.331374853114</v>
       </c>
     </row>
-    <row r="263" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:29">
       <c r="A263" s="2">
         <v>45200</v>
       </c>
@@ -23090,7 +23106,7 @@
         <v>105.28789659224439</v>
       </c>
     </row>
-    <row r="264" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:29">
       <c r="A264" s="2">
         <v>45231</v>
       </c>
@@ -23176,7 +23192,7 @@
         <v>97.767332549941273</v>
       </c>
     </row>
-    <row r="265" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:29">
       <c r="A265" s="2">
         <v>45261</v>
       </c>
@@ -23262,7 +23278,7 @@
         <v>146.76850763807289</v>
       </c>
     </row>
-    <row r="266" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:29">
       <c r="A266" s="2">
         <v>45292</v>
       </c>
@@ -23348,7 +23364,7 @@
         <v>156.05170387779091</v>
       </c>
     </row>
-    <row r="267" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:29">
       <c r="A267" s="2">
         <v>45323</v>
       </c>
@@ -23434,7 +23450,7 @@
         <v>136.07520564042309</v>
       </c>
     </row>
-    <row r="268" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:29">
       <c r="A268" s="2">
         <v>45352</v>
       </c>
@@ -23520,7 +23536,7 @@
         <v>124.4418331374853</v>
       </c>
     </row>
-    <row r="269" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:29">
       <c r="A269" s="2">
         <v>45383</v>
       </c>
@@ -23606,7 +23622,7 @@
         <v>113.9835487661575</v>
       </c>
     </row>
-    <row r="270" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:29">
       <c r="A270" s="2">
         <v>45413</v>
       </c>
@@ -23692,7 +23708,7 @@
         <v>109.753231492362</v>
       </c>
     </row>
-    <row r="271" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:29">
       <c r="A271" s="2">
         <v>45444</v>
       </c>
@@ -23778,7 +23794,7 @@
         <v>105.64042303172739</v>
       </c>
     </row>
-    <row r="272" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:29">
       <c r="A272" s="2">
         <v>45474</v>
       </c>
@@ -23864,7 +23880,7 @@
         <v>103.2902467685077</v>
       </c>
     </row>
-    <row r="273" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:29">
       <c r="A273" s="2">
         <v>45505</v>
       </c>
@@ -23950,7 +23966,7 @@
         <v>102.4676850763807</v>
       </c>
     </row>
-    <row r="274" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:29">
       <c r="A274" s="2">
         <v>45536</v>
       </c>
@@ -24036,7 +24052,7 @@
         <v>101.0575793184489</v>
       </c>
     </row>
-    <row r="275" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:29">
       <c r="A275" s="2">
         <v>45566</v>
       </c>
@@ -24122,7 +24138,7 @@
         <v>98.707403055229165</v>
       </c>
     </row>
-    <row r="276" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:29">
       <c r="A276" s="2">
         <v>45597</v>
       </c>
@@ -24208,7 +24224,7 @@
         <v>96.004700352526456</v>
       </c>
     </row>
-    <row r="277" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:29">
       <c r="A277" s="2">
         <v>45627</v>
       </c>
